--- a/data/trans_orig/P13A_1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>36658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>563</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>563</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>405</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>406</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,27 +2475,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>483</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>484</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>48419</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>40497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>51746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50784</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>799</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>52498</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>52498</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>52498</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>50965</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50965</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50965</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3161,27 +3161,27 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3196,27 +3196,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>155080</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134306</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>147895</t>
+          <t>159931</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>171861</t>
+          <t>185120</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>185399</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
